--- a/Dados/Ativos_Sem_Codigo.xlsx
+++ b/Dados/Ativos_Sem_Codigo.xlsx
@@ -34,13 +34,13 @@
     <t>COD_XP</t>
   </si>
   <si>
-    <t>CDB</t>
-  </si>
-  <si>
-    <t>CDB3251WXH0</t>
-  </si>
-  <si>
-    <t>REAL FIM</t>
+    <t>LFSN</t>
+  </si>
+  <si>
+    <t>LFSN19001BC</t>
+  </si>
+  <si>
+    <t>FIRF GERAES 30</t>
   </si>
 </sst>
 </file>
@@ -433,7 +433,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="2">
-        <v>46454</v>
+        <v>46486</v>
       </c>
       <c r="D2" t="s">
         <v>8</v>

--- a/Dados/Ativos_Sem_Codigo.xlsx
+++ b/Dados/Ativos_Sem_Codigo.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
   <si>
     <t>Sub Classe</t>
   </si>
@@ -34,13 +34,19 @@
     <t>COD_XP</t>
   </si>
   <si>
-    <t>LFSN</t>
-  </si>
-  <si>
-    <t>LFSN19001BC</t>
-  </si>
-  <si>
-    <t>FIRF GERAES 30</t>
+    <t>LFSC</t>
+  </si>
+  <si>
+    <t>LFSC19002CE</t>
+  </si>
+  <si>
+    <t>LFSC19002HS</t>
+  </si>
+  <si>
+    <t>LFSC19002CD</t>
+  </si>
+  <si>
+    <t>JERA2026 FIM</t>
   </si>
 </sst>
 </file>
@@ -402,7 +408,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -433,10 +439,38 @@
         <v>7</v>
       </c>
       <c r="C2" s="2">
-        <v>46486</v>
+        <v>47217</v>
       </c>
       <c r="D2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
         <v>8</v>
+      </c>
+      <c r="C3" s="2">
+        <v>47217</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2">
+        <v>47217</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/Dados/Ativos_Sem_Codigo.xlsx
+++ b/Dados/Ativos_Sem_Codigo.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="23">
   <si>
     <t>Sub Classe</t>
   </si>
@@ -34,19 +34,55 @@
     <t>COD_XP</t>
   </si>
   <si>
-    <t>LFSC</t>
-  </si>
-  <si>
-    <t>LFSC19002CE</t>
-  </si>
-  <si>
-    <t>LFSC19002HS</t>
-  </si>
-  <si>
-    <t>LFSC19002CD</t>
-  </si>
-  <si>
-    <t>JERA2026 FIM</t>
+    <t>LFSN</t>
+  </si>
+  <si>
+    <t>Letra Financeira</t>
+  </si>
+  <si>
+    <t>CDB</t>
+  </si>
+  <si>
+    <t>LFSN2200B4M</t>
+  </si>
+  <si>
+    <t>LFSN2200GD7</t>
+  </si>
+  <si>
+    <t>LF002600MB0</t>
+  </si>
+  <si>
+    <t>LF00260094N</t>
+  </si>
+  <si>
+    <t>LF002600MAZ</t>
+  </si>
+  <si>
+    <t>LF002600MB1</t>
+  </si>
+  <si>
+    <t>CDB8265ICFW</t>
+  </si>
+  <si>
+    <t>CDB8265ICFZ</t>
+  </si>
+  <si>
+    <t>CDB8265ICFV</t>
+  </si>
+  <si>
+    <t>CDB8265ICFY</t>
+  </si>
+  <si>
+    <t>CDB8265ICFX</t>
+  </si>
+  <si>
+    <t>FIRF GERAES</t>
+  </si>
+  <si>
+    <t>FIRF GERAES 30</t>
+  </si>
+  <si>
+    <t>HORIZONTE FIM</t>
   </si>
 </sst>
 </file>
@@ -408,7 +444,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -436,13 +472,13 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C2" s="2">
-        <v>47217</v>
+        <v>48500</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -450,13 +486,13 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C3" s="2">
-        <v>47217</v>
+        <v>48570</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -467,10 +503,178 @@
         <v>9</v>
       </c>
       <c r="C4" s="2">
-        <v>47217</v>
+        <v>48500</v>
       </c>
       <c r="D4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
         <v>10</v>
+      </c>
+      <c r="C5" s="2">
+        <v>48570</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="2">
+        <v>48500</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="2">
+        <v>48570</v>
+      </c>
+      <c r="D7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="2">
+        <v>46965</v>
+      </c>
+      <c r="D8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="2">
+        <v>46839</v>
+      </c>
+      <c r="D9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="2">
+        <v>46965</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="2">
+        <v>46965</v>
+      </c>
+      <c r="D11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="2">
+        <v>46359</v>
+      </c>
+      <c r="D12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="2">
+        <v>46359</v>
+      </c>
+      <c r="D13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="2">
+        <v>46359</v>
+      </c>
+      <c r="D14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="2">
+        <v>46359</v>
+      </c>
+      <c r="D15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="2">
+        <v>46359</v>
+      </c>
+      <c r="D16" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
